--- a/public/files/Data_By_Towns_Index/Burlington/Tabernacle Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Tabernacle Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,168 +425,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PATEL, MILIND D &amp; RIYA M</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GUPTA, ASEEM &amp; CAPANESCU, CRISTINA</t>
+          <t>6 GRANDE BLVD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>846 POWELL ROAD</t>
+          <t>Tabernacle Township</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tabernacle Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39.8709949</v>
+        <v>-74.7539733</v>
       </c>
       <c r="G2" t="n">
-        <v>-74.66613649999999</v>
+        <v>39.8540185</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJKzoP2Tw6wYkRQwlhh5xvFT4</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SHETH, NILAY G &amp; PRITI N &amp; SHETH, R</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PATEL, MILIND D &amp; RIYA M</t>
+          <t>8 GRANDE BLVD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6 GRANDE BLVD</t>
+          <t>Tabernacle Township</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tabernacle Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>39.8540185</v>
+        <v>-74.7538866</v>
       </c>
       <c r="G3" t="n">
-        <v>-74.7539733</v>
+        <v>39.85446290000001</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJ_Wml1jw6wYkR2Ao_Um5mQAA</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATEL,VIJAY &amp; SUSHILA</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PATEL,VIJAY &amp; SUSHILA</t>
+          <t>13 HIDDEN ACRES DRIVE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13 HIDDEN ACRES DRIVE</t>
+          <t>Tabernacle Township</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tabernacle Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>-74.7442228</v>
+      </c>
+      <c r="G4" t="n">
         <v>39.8405897</v>
       </c>
-      <c r="G4" t="n">
-        <v>-74.7442228</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SHETH, NILAY G &amp; PRITI N &amp; SHETH, R</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8 GRANDE BLVD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Tabernacle Township</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sheth</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>39.85446290000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-74.7538866</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJfasMjEg6wYkReQj6ZAL69AI</t>
+        </is>
       </c>
     </row>
   </sheetData>
